--- a/feedback_surveys/027_evening_reflection_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/027_evening_reflection_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very_stressed</t>
+          <t>very stressed</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>somewhat_stressed</t>
+          <t>somewhat stressed</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>not_at_all_stressed</t>
+          <t>not at all stressed</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>get_outside</t>
+          <t>get outside</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>listen_to_music</t>
+          <t>listen to music</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>talk_to_friends</t>
+          <t>talk to friends</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>take_a_nap</t>
+          <t>take a nap</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>watch_a_comedy_movie</t>
+          <t>watch a comedy movie</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>get_a_massage</t>
+          <t>get a massage</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>read_a_book</t>
+          <t>read a book</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>get_enough_sleep</t>
+          <t>get enough sleep</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>get_enough_sleep</t>
+          <t>get enough sleep</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>get_outside</t>
+          <t>get outside</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eat_nourishing_food</t>
+          <t>eat nourishing food</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>stay_hydrated</t>
+          <t>stay hydrated</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>listen_to_music</t>
+          <t>listen to music</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>spend_time_with_loved_ones</t>
+          <t>spend time with loved ones</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>take_a_nap</t>
+          <t>take a nap</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>do_a_hobby</t>
+          <t>do a hobby</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>watch_a_comedy_movie</t>
+          <t>watch a comedy movie</t>
         </is>
       </c>
     </row>
